--- a/profiles-web/assets/profile-form.xlsx
+++ b/profiles-web/assets/profile-form.xlsx
@@ -317,7 +317,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉼표로 구분, 5~10개  예) 기계학습, 표현학습, 자기지도학습, 멀티모달, 신뢰가능 AI</t>
+          <t xml:space="preserve">쉼표로 구분, 3~5개  예) 기계학습, 표현학습, 멀티모달</t>
         </is>
       </c>
     </row>

--- a/profiles-web/assets/profile-form.xlsx
+++ b/profiles-web/assets/profile-form.xlsx
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -42,6 +42,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF666666"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -99,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -116,6 +123,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -127,9 +140,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -140,447 +154,536 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">노란 칸(B열)에 입력해 주세요. 여러 줄 항목은 칸 하나에 하나씩 쓰고, 칸이 모자라면 바로 아래에 행을 삽입하세요.
-작성한 이 파일과 사진(그림)을 소속 기관 메일로 example@kiise.or.kr 에 보내 주세요.</t>
+          <t xml:space="preserve">노란 칸(C열)에 입력해 주세요. '필수' 항목은 꼭 채워 주시고, '선택' 항목은 비워 두셔도 됩니다.
+여러 줄 항목은 칸 하나에 하나씩 적어 주세요. 작성한 이 파일과 사진(그림)을 소속 기관 메일로 example@kiise.or.kr 에 보내 주세요.</t>
         </is>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">구분</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">항목</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">내용 (이 열에 입력)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">안내</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">성명(국문)</t>
         </is>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">예) 김정보</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">성명(영문)</t>
         </is>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">예) Jeongbo Kim — 프로필 주소를 만드는 데 쓰입니다</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">소속 기관</t>
         </is>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">예) ○○대학교</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">소속 학과/학부</t>
         </is>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4"/>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">예) 컴퓨터공학과</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">직위</t>
         </is>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">목록에서 고르거나 직접 입력</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">최종 학위</t>
         </is>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4"/>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">예) ○○대학교 공학박사 (인공지능)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">최초 임용일</t>
         </is>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">예) 2024-03</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">E-mail</t>
         </is>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프로필에 공개되는 연락처. 나중에 수정 양식을 보내실 때도 같은 주소로 적어 주세요</t>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로필에 공개되는 연락처. 수정 양식을 보내실 때도 같은 주소로 적어 주세요</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">연구실 홈페이지</t>
         </is>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선택 — 없으면 비워 두세요</t>
-        </is>
-      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">추가 링크</t>
         </is>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선택 — 칸 하나에 하나, 라벨|주소  예) Google Scholar|https://scholar.google.com/…</t>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칸 하나에 하나, 라벨|주소  예) Google Scholar|https://scholar.google.com/…</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">연구 키워드</t>
         </is>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4"/>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">쉼표로 구분, 3~5개  예) 기계학습, 표현학습, 멀티모달</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">소사이어티·연구회</t>
         </is>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4"/>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">정보과학회 내 소속. '소사이어티 목록' 시트의 이름 그대로, 쉼표로 구분</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주로 참석하는 학회</t>
-        </is>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쉼표로 구분  예) NeurIPS, ICML, 한국소프트웨어종합학술대회(KSC)</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인사말</t>
+        </is>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동료 연구자들께 전하는 인사, 120자 이내</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한마디</t>
-        </is>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선택 — 120자 이내, 동료 연구자들께 전하고 싶은 한 문장</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주요 경력</t>
+        </is>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현 직위, 이전 소속, 학위 등. 칸 하나에 하나, 모자라면 아래에 행 삽입</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주요 경력</t>
-        </is>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이력 중심 — 현 직위, 이전 소속, 학위 등. 칸 하나에 하나, 모자라면 아래에 행 삽입</t>
-        </is>
-      </c>
+      <c r="A20" s="6"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
     </row>
     <row r="21">
-      <c r="A21" s="3"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
     </row>
     <row r="22">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
     </row>
     <row r="23">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="5"/>
     </row>
     <row r="24">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대표 논문</t>
+        </is>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칸 하나에 한 편, 최대 5편</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대표 논문 및 수행과제</t>
-        </is>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실적 중심 — 주저자 논문, 수행 과제, 특허, 수상 등</t>
-        </is>
-      </c>
+      <c r="A25" s="7"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="5"/>
     </row>
     <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="5"/>
     </row>
     <row r="27">
-      <c r="A27" s="3"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="5"/>
     </row>
     <row r="28">
-      <c r="A28" s="3"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="5"/>
     </row>
     <row r="29">
-      <c r="A29" s="3"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수행과제</t>
+        </is>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칸 하나에 한 건, 최대 5건</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">연구목표</t>
-        </is>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">칸 하나에 목표 하나</t>
-        </is>
-      </c>
+      <c r="A30" s="7"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="5"/>
     </row>
     <row r="31">
-      <c r="A31" s="3"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="5"/>
     </row>
     <row r="32">
-      <c r="A32" s="3"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="5"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">연구내용</t>
-        </is>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">칸 하나가 한 문단</t>
-        </is>
-      </c>
+      <c r="A33" s="7"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="5"/>
     </row>
     <row r="34">
-      <c r="A34" s="3"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연구목표 및 내용</t>
+        </is>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">칸 하나에 한 문단, 최대 5개</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="3"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="5"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공동연구 희망분야</t>
-        </is>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">협력 가능한 분야·데이터·기술</t>
-        </is>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="5"/>
     </row>
     <row r="37">
-      <c r="A37" s="3"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="5"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
     </row>
     <row r="38">
-      <c r="A38" s="3"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="5"/>
+      <c r="A38" s="6"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">사진 파일명</t>
         </is>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="4"/>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">메일에 첨부한 사진의 파일 이름  예) kim.jpg — 세로 3:4, JPG·PNG</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그림1 파일명</t>
-        </is>
-      </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선택 — 연구내용 그림(가로형 권장)을 첨부했다면 파일 이름</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그림 파일명</t>
+        </is>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연구내용 그림 1장(가로형 권장)을 첨부했다면 그 파일 이름</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그림1 설명</t>
-        </is>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">선택</t>
         </is>
       </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그림 설명</t>
+        </is>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그림 아래에 붙는 한 줄 설명</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그림2 파일명</t>
-        </is>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선택 — 그림이 많으면 A4 한 면을 넘습니다. 최대 2장</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공개 동의</t>
+        </is>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위 내용을 신진연구자 브로셔에 공개하는 데 동의하시면 '동의'라고 적어 주세요</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그림2 설명</t>
-        </is>
-      </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선택</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공개 동의</t>
-        </is>
-      </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위 내용을 신진연구자 브로셔에 공개하는 데 동의하시면 '동의'라고 적어 주세요</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담당자</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">프로필 id</t>
         </is>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C43" s="4"/>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">담당자용 — 비워 두세요</t>
         </is>
@@ -588,14 +691,14 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="B8">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="C8">
       <formula1>"조교수,부교수,교수,연구교수,선임연구원,책임연구원"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="B44">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="C42">
       <formula1>"동의"</formula1>
     </dataValidation>
   </dataValidations>

--- a/profiles-web/assets/profile-form.xlsx
+++ b/profiles-web/assets/profile-form.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">수행과제</t>
+          <t xml:space="preserve">수행 과제</t>
         </is>
       </c>
       <c r="C29" s="4"/>
@@ -565,7 +565,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">연구목표 및 내용</t>
+          <t xml:space="preserve">연구 목표 및 내용</t>
         </is>
       </c>
       <c r="C34" s="4"/>
@@ -631,7 +631,7 @@
       <c r="C40" s="4"/>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">연구내용 그림 1장(가로형 권장)을 첨부했다면 그 파일 이름</t>
+          <t xml:space="preserve">연구 내용 그림 1장(가로형 권장)을 첨부했다면 그 파일 이름</t>
         </is>
       </c>
     </row>
